--- a/data/trans_bre/P1408-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1408-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-40,42%</t>
+          <t>-37,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -2,06</t>
+          <t>-6,18; -2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -1,16</t>
+          <t>-4,67; -1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,24</t>
+          <t>-3,98; -0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; -1,35</t>
+          <t>-6,08; -1,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,76; -26,93</t>
+          <t>-61,38; -28,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,97; -28,93</t>
+          <t>-71,4; -28,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,88; -1,9</t>
+          <t>-69,78; -10,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,09; -17,62</t>
+          <t>-56,99; -14,54</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,3</t>
+          <t>-1,48; 0,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,01</t>
+          <t>-1,43; -0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,1</t>
+          <t>-1,23; 0,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,36</t>
+          <t>-0,21; 1,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 20,29</t>
+          <t>-56,56; 26,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 5,61</t>
+          <t>-82,4; 6,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 12,12</t>
+          <t>-67,43; 14,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 151,63</t>
+          <t>-15,01; 115,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,23</t>
+          <t>-1,48; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,77</t>
+          <t>-1,24; 0,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,99</t>
+          <t>-0,78; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,76; 173,24</t>
+          <t>-83,29; 225,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 174,96</t>
+          <t>-58,0; 179,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,53</t>
+          <t>-2,3; -0,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,28</t>
+          <t>-1,66; -0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,08</t>
+          <t>-1,31; -0,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,76</t>
+          <t>-0,67; 0,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -14,79</t>
+          <t>-50,59; -16,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,84; -15,35</t>
+          <t>-62,31; -17,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,84; -1,86</t>
+          <t>-56,17; -1,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 37,7</t>
+          <t>-22,63; 30,5</t>
         </is>
       </c>
     </row>
